--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_26_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_26_R3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.997</v>
+        <v>3.7179</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4426</v>
+        <v>4.6008</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4457</v>
+        <v>-0.8829</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3804</v>
+        <v>0.6823</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7487</v>
+        <v>2.7332</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3683</v>
+        <v>-2.0509</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5744</v>
+        <v>2.9406</v>
       </c>
       <c r="K2" t="n">
-        <v>2.464</v>
+        <v>3.6166</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1104</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1941</v>
+        <v>-2.2583</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7153</v>
+        <v>-0.8834</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4787</v>
+        <v>-1.375</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2275</v>
+        <v>1.033</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1181</v>
+        <v>0.7631</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1094</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9304</v>
+        <v>2.0026</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7501</v>
+        <v>3.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.6805</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4443</v>
+        <v>3.645</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1591</v>
+        <v>4.7627</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7148</v>
+        <v>-1.1177</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6823</v>
+        <v>1.1152</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7332</v>
+        <v>1.0717</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0509</v>
+        <v>0.0435</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9406</v>
+        <v>3.227</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6166</v>
+        <v>1.8086</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.4184</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2583</v>
+        <v>-2.1119</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8834</v>
+        <v>-0.7369</v>
       </c>
       <c r="O3" t="n">
         <v>-1.375</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7594</v>
+        <v>0.2978</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3214</v>
+        <v>0.4092</v>
       </c>
       <c r="U3" t="n">
-        <v>0.438</v>
+        <v>-0.1114</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0026</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2166</v>
+        <v>2.2862</v>
       </c>
       <c r="X3" t="n">
         <v>-1.214</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8285</v>
+        <v>3.1583</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3158</v>
+        <v>5.7048</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4874</v>
+        <v>-2.5465</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1152</v>
+        <v>0.3804</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0717</v>
+        <v>1.7487</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0435</v>
+        <v>-1.3683</v>
       </c>
       <c r="J4" t="n">
-        <v>3.227</v>
+        <v>2.5744</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8086</v>
+        <v>2.464</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4184</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1119</v>
+        <v>-2.1941</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7369</v>
+        <v>-0.7153</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.375</v>
+        <v>-1.4787</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5187</v>
+        <v>1.3888</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0376</v>
+        <v>1.3803</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.481</v>
+        <v>0.0086</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2862</v>
+        <v>1.7501</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.536</v>
+        <v>0.597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.463</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4709</v>
+        <v>0.134</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2905</v>
+        <v>-0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6468</v>
+        <v>1.6599</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9373</v>
+        <v>-1.7599</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0653</v>
+        <v>1.9368</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1833</v>
+        <v>2.0607</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2486</v>
+        <v>-0.1239</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2252</v>
+        <v>-2.0368</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5365</v>
+        <v>-0.4008</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3113</v>
+        <v>-1.636</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1486</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6122</v>
+        <v>0.8456</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5364</v>
+        <v>0.0833</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1184</v>
+        <v>0.3811</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1524</v>
+        <v>-0.9218</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.034</v>
+        <v>1.3029</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1</v>
+        <v>-1.2905</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6599</v>
+        <v>0.6468</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7599</v>
+        <v>-1.9373</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9368</v>
+        <v>-1.0653</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0607</v>
+        <v>1.1833</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1239</v>
+        <v>-2.2486</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0368</v>
+        <v>-0.2252</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4008</v>
+        <v>-0.5365</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.636</v>
+        <v>0.3113</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4503</v>
+        <v>0.9937</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5351</v>
+        <v>0.6253</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0848</v>
+        <v>0.3684</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9542</v>
+        <v>-0.7355</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9054</v>
+        <v>1.0233</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8596</v>
+        <v>-1.7588</v>
       </c>
       <c r="G8" t="n">
         <v>1.115</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8527</v>
+        <v>-0.6339</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3636</v>
+        <v>-1.2114</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9106</v>
+        <v>-0.5568</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.453</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.855</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3137</v>
+        <v>0.4659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.4107</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7501</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2845</v>
+        <v>-2.4691</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3845</v>
+        <v>0.162</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9</v>
+        <v>-2.6311</v>
       </c>
       <c r="G10" t="n">
         <v>0.0437</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2713</v>
+        <v>-0.456</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.275</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4498</v>
+        <v>-0.181</v>
       </c>
       <c r="V10" t="n">
         <v>-3.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5312</v>
+        <v>-3.5458</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9629</v>
+        <v>-4.7087</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4317</v>
+        <v>1.1629</v>
       </c>
       <c r="G11" t="n">
         <v>-5.962</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2855</v>
+        <v>0.6998</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8136</v>
+        <v>0.4406</v>
       </c>
       <c r="U11" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V11" t="n">
         <v>0.7886</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4876</v>
+        <v>5.234400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4212</v>
+        <v>11.1681</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.933799999999999</v>
+        <v>-5.9338</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.8882</v>
+        <v>-4.888199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>5.634399999999999</v>
@@ -1390,10 +1390,10 @@
         <v>16.2367</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7576</v>
+        <v>5.5043</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5802</v>
+        <v>4.327000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.1774</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6096</v>
+        <v>2.5487</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4997</v>
+        <v>3.6176</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8901</v>
+        <v>-1.0689</v>
       </c>
       <c r="G14" t="n">
         <v>1.9557</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3497</v>
+        <v>0.2888</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1221</v>
+        <v>0.2401</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2276</v>
+        <v>0.0488</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="E15" t="n">
-        <v>1.087</v>
+        <v>0.9691</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4857</v>
+        <v>-0.1941</v>
       </c>
       <c r="G15" t="n">
         <v>0.192</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9129</v>
+        <v>-0.7391</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.803</v>
+        <v>-0.5113</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0561</v>
+        <v>-0.9217</v>
       </c>
       <c r="E16" t="n">
         <v>-0.2092</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8469</v>
+        <v>-0.7124</v>
       </c>
       <c r="G16" t="n">
         <v>1.0887</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.449</v>
+        <v>-0.3145</v>
       </c>
       <c r="T16" t="n">
         <v>-0.224</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4363</v>
+        <v>-1.0362</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1155</v>
+        <v>-2.1628</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3207</v>
+        <v>1.1266</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4417</v>
+        <v>-0.3245</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9532</v>
+        <v>-1.1811</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4885</v>
+        <v>0.8566</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5156</v>
+        <v>-0.8027</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7661</v>
+        <v>-0.7156</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.0871</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9261</v>
+        <v>0.4781</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1871</v>
+        <v>-0.4655</v>
       </c>
       <c r="O17" t="n">
-        <v>0.261</v>
+        <v>0.9436</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>1.093</v>
+        <v>-0.4797</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7196</v>
+        <v>-0.2003</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3734</v>
+        <v>-0.2794</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.508</v>
+        <v>-1.5542</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6346</v>
+        <v>-1.2335</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1266</v>
+        <v>-0.3207</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3245</v>
+        <v>-2.4417</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1811</v>
+        <v>-1.9532</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8566</v>
+        <v>-0.4885</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8027</v>
+        <v>-1.5156</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7156</v>
+        <v>-0.7661</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0871</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4781</v>
+        <v>-0.9261</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4655</v>
+        <v>-1.1871</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9436</v>
+        <v>0.261</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9515</v>
+        <v>0.975</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6721</v>
+        <v>0.6016</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2794</v>
+        <v>0.3734</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6564</v>
+        <v>-1.5698</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2146</v>
+        <v>-0.0092</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8709</v>
+        <v>-1.5606</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2529</v>
+        <v>-0.8617</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1011</v>
+        <v>-1.1595</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1518</v>
+        <v>0.2978</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1975</v>
+        <v>0.0536</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9326</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2649</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9446</v>
+        <v>-0.9153</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8314</v>
+        <v>-1.1763</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8868</v>
+        <v>0.261</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5718</v>
+        <v>0.06</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5579</v>
+        <v>0.1691</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0139</v>
+        <v>-0.1092</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7049</v>
+        <v>-1.6513</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2451</v>
+        <v>-0.1393</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4598</v>
+        <v>-1.512</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8617</v>
+        <v>3.2529</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1595</v>
+        <v>0.1011</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2978</v>
+        <v>3.1518</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0536</v>
+        <v>4.1975</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0168</v>
+        <v>1.9326</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>2.2649</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9153</v>
+        <v>-0.9446</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1763</v>
+        <v>-1.8314</v>
       </c>
       <c r="O20" t="n">
-        <v>0.261</v>
+        <v>0.8868</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0751</v>
+        <v>-1.5668</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0668</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0083</v>
+        <v>-0.655</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7459</v>
+        <v>-1.9089</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2827</v>
+        <v>-0.0712</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0286</v>
+        <v>-1.8377</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3457</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2921</v>
+        <v>-0.4551</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4604</v>
+        <v>0.1065</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.5616</v>
       </c>
       <c r="V22" t="n">
         <v>0.8197</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4685</v>
+        <v>-4.2605</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7015</v>
+        <v>-2.5836</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.767</v>
+        <v>-1.6769</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8845</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7644</v>
+        <v>-0.5564</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1669</v>
+        <v>-0.0769</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3558</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.487400000000001</v>
+        <v>-3.701099999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>5.792100000000001</v>
+        <v>5.791899999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.2792</v>
+        <v>-9.492800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>4.8881</v>
@@ -2326,13 +2326,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.7576</v>
+        <v>-3.971299999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1773</v>
+        <v>-1.1774</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5801</v>
+        <v>-2.7939</v>
       </c>
       <c r="V24" t="n">
         <v>3.500200000000001</v>
